--- a/17 18 20/Excel/03.Pivot Tables & Data Analysis/Data Analysis.xlsx
+++ b/17 18 20/Excel/03.Pivot Tables & Data Analysis/Data Analysis.xlsx
@@ -18,10 +18,11 @@
     <sheet name="RawDATA" sheetId="16" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Grouping of Rows'!$A$1:$D$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Grouping of Rows'!$A$1:$D$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RawDATA!$A$1:$K$54</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="180">
   <si>
     <t>passanger</t>
   </si>
@@ -237,45 +238,24 @@
     <t>First Three</t>
   </si>
   <si>
-    <t>Last Thre</t>
-  </si>
-  <si>
     <t>Monday</t>
   </si>
   <si>
-    <t>Mon</t>
-  </si>
-  <si>
     <t>Tuesday</t>
   </si>
   <si>
-    <t>Tue</t>
-  </si>
-  <si>
     <t>Wednesday</t>
   </si>
   <si>
-    <t>Wed</t>
-  </si>
-  <si>
     <t>Thursday</t>
   </si>
   <si>
-    <t>Thu</t>
-  </si>
-  <si>
     <t>Friday</t>
   </si>
   <si>
-    <t>Fri</t>
-  </si>
-  <si>
     <t>Saturday</t>
   </si>
   <si>
-    <t>Sat</t>
-  </si>
-  <si>
     <t>Text Example</t>
   </si>
   <si>
@@ -511,6 +491,87 @@
   </si>
   <si>
     <t>canada</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>2027</t>
+  </si>
+  <si>
+    <t>2028</t>
+  </si>
+  <si>
+    <t>2029</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>ay</t>
+  </si>
+  <si>
+    <t>mon</t>
+  </si>
+  <si>
+    <t>tue</t>
+  </si>
+  <si>
+    <t>wed</t>
+  </si>
+  <si>
+    <t>thu</t>
+  </si>
+  <si>
+    <t>fri</t>
+  </si>
+  <si>
+    <t>sat</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>MON</t>
+  </si>
+  <si>
+    <t>TUE</t>
+  </si>
+  <si>
+    <t>WED</t>
+  </si>
+  <si>
+    <t>THU</t>
+  </si>
+  <si>
+    <t>FRI</t>
+  </si>
+  <si>
+    <t>SAT</t>
   </si>
 </sst>
 </file>
@@ -1144,9 +1205,15 @@
       <c r="B2" s="10">
         <v>45292</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="C2" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>159</v>
+      </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
@@ -1161,9 +1228,15 @@
       <c r="B3" s="10">
         <v>45659</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
+      <c r="C3" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>160</v>
+      </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -1178,9 +1251,15 @@
       <c r="B4" s="10">
         <v>46025</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
+      <c r="C4" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>161</v>
+      </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -1195,9 +1274,15 @@
       <c r="B5" s="10">
         <v>46391</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
+      <c r="C5" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>162</v>
+      </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -1212,9 +1297,15 @@
       <c r="B6" s="10">
         <v>46757</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+      <c r="C6" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>163</v>
+      </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
@@ -1229,9 +1320,15 @@
       <c r="B7" s="10">
         <v>47124</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
+      <c r="C7" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>164</v>
+      </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
@@ -1260,7 +1357,7 @@
         <v>65</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>66</v>
@@ -1269,15 +1366,9 @@
         <v>67</v>
       </c>
       <c r="F9" s="7"/>
-      <c r="G9" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>67</v>
-      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
     </row>
@@ -1286,15 +1377,21 @@
         <v>101</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+        <v>68</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>167</v>
+      </c>
       <c r="F10" s="7"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
@@ -1303,15 +1400,21 @@
         <v>102</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
+        <v>69</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>168</v>
+      </c>
       <c r="F11" s="7"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
     </row>
@@ -1320,15 +1423,21 @@
         <v>103</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>169</v>
+      </c>
       <c r="F12" s="7"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
     </row>
@@ -1337,15 +1446,21 @@
         <v>104</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+        <v>71</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>170</v>
+      </c>
       <c r="F13" s="7"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
     </row>
@@ -1354,15 +1469,21 @@
         <v>105</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>171</v>
+      </c>
       <c r="F14" s="7"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
     </row>
@@ -1371,15 +1492,21 @@
         <v>106</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>172</v>
+      </c>
       <c r="F15" s="7"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
     </row>
@@ -1401,13 +1528,13 @@
         <v>60</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>63</v>
@@ -1424,16 +1551,16 @@
         <v>101</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="D18" s="6">
         <v>101</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>70</v>
+        <v>174</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -1447,16 +1574,16 @@
         <v>102</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="D19" s="6">
         <v>102</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -1470,16 +1597,16 @@
         <v>103</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="D20" s="6">
         <v>103</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>74</v>
+        <v>176</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -1493,16 +1620,16 @@
         <v>104</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="D21" s="6">
         <v>104</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -1516,16 +1643,16 @@
         <v>105</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="D22" s="6">
         <v>105</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>78</v>
+        <v>178</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
@@ -1539,16 +1666,16 @@
         <v>106</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="D23" s="6">
         <v>106</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
@@ -1746,8 +1873,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="3" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.77734375" bestFit="1" customWidth="1"/>
@@ -1766,7 +1893,7 @@
         <v>11</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1777,7 +1904,7 @@
       <c r="C2" s="38"/>
       <c r="D2" s="41"/>
     </row>
-    <row r="3" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A3" s="40"/>
       <c r="B3" s="21" t="s">
         <v>35</v>
@@ -1785,7 +1912,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="23"/>
     </row>
-    <row r="4" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A4" s="40"/>
       <c r="B4" s="21"/>
       <c r="C4" s="22" t="s">
@@ -1795,7 +1922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A5" s="40"/>
       <c r="B5" s="21"/>
       <c r="C5" s="22" t="s">
@@ -1805,7 +1932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A6" s="40"/>
       <c r="B6" s="21" t="s">
         <v>24</v>
@@ -1813,268 +1940,278 @@
       <c r="C6" s="22"/>
       <c r="D6" s="23"/>
     </row>
-    <row r="7" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A7" s="40"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D7" s="23">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="29" t="s">
+    <row r="8" spans="1:4" hidden="1" outlineLevel="3" x14ac:dyDescent="0.3">
+      <c r="A8" s="40"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="32">
-        <f>COUNTIF(RawDATA!I:I,'Grouping of Rows'!A8)</f>
+      <c r="B9" s="30"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="32">
+        <f>COUNTIF(RawDATA!I:I,'Grouping of Rows'!A9)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="15"/>
-      <c r="B9" s="13" t="s">
+    <row r="10" spans="1:4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A10" s="15"/>
+      <c r="B10" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17">
+      <c r="C10" s="16"/>
+      <c r="D10" s="17">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="15"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="17"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A11" s="15"/>
       <c r="B11" s="13"/>
       <c r="C11" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="17"/>
+    </row>
+    <row r="12" spans="1:4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A12" s="15"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D12" s="17">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="15"/>
-      <c r="B12" s="13" t="s">
+    <row r="13" spans="1:4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A13" s="15"/>
+      <c r="B13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="17"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="15"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+    </row>
+    <row r="14" spans="1:4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="13"/>
       <c r="C14" s="16" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D14" s="17">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A15" s="15"/>
       <c r="B15" s="13"/>
       <c r="C15" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A16" s="15"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D16" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="15"/>
-      <c r="B16" s="13" t="s">
+    <row r="17" spans="1:4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A17" s="15"/>
+      <c r="B17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="17"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="15"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+    </row>
+    <row r="18" spans="1:4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="13"/>
       <c r="C18" s="16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D18" s="17">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A19" s="15"/>
       <c r="B19" s="13"/>
       <c r="C19" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D19" s="17">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="20">
-        <f>COUNTIF(RawDATA!I:I,'Grouping of Rows'!A20)</f>
+    <row r="20" spans="1:4" hidden="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A20" s="15"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="14"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="20">
+        <f>COUNTIF(RawDATA!I:I,'Grouping of Rows'!A21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="18"/>
-      <c r="B21" s="14" t="s">
+    <row r="22" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="18"/>
+      <c r="B22" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="20"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="18"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="19" t="s">
-        <v>48</v>
-      </c>
+      <c r="C22" s="19"/>
       <c r="D22" s="20"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A23" s="18"/>
       <c r="B23" s="14"/>
       <c r="C23" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="D23" s="20"/>
+    </row>
+    <row r="24" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A24" s="18"/>
       <c r="B24" s="14"/>
       <c r="C24" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D25" s="20">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="18"/>
-      <c r="B25" s="14" t="s">
+    <row r="26" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="B26" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="20">
+      <c r="C26" s="19"/>
+      <c r="D26" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="18"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="20"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18"/>
       <c r="B27" s="14"/>
       <c r="C27" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="20"/>
+    </row>
+    <row r="28" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="18"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="20">
+      <c r="D28" s="20">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="18"/>
-      <c r="B28" s="14" t="s">
+    <row r="29" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="18"/>
+      <c r="B29" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="20"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="18"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="19"/>
+      <c r="D29" s="20"/>
+    </row>
+    <row r="30" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="18"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D30" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="36" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="37"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="39"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="40"/>
-      <c r="B31" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="23"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="39"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="40"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="22" t="s">
+      <c r="B32" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="22"/>
+      <c r="D32" s="23"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="40"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="23"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="24"/>
-      <c r="B33" s="21" t="s">
+      <c r="D33" s="23"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="24"/>
+      <c r="B34" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="22"/>
-      <c r="D33" s="23"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="25"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="22"/>
+      <c r="D34" s="23"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="25"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="28">
+      <c r="D35" s="28">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D34"/>
+  <autoFilter ref="A1:D35"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2108,13 +2245,13 @@
         <v>51</v>
       </c>
       <c r="B1" s="42" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C1" s="42" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E1" t="s">
         <v>6</v>
@@ -2138,7 +2275,7 @@
         <v>52</v>
       </c>
       <c r="L1" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="P1" t="s">
         <v>50</v>
@@ -2167,13 +2304,13 @@
         <v>42415</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -2185,7 +2322,7 @@
         <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I2" t="s">
         <v>25</v>
@@ -2226,13 +2363,13 @@
         <v>42490</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
@@ -2244,7 +2381,7 @@
         <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I3" t="s">
         <v>25</v>
@@ -2285,13 +2422,13 @@
         <v>42520</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
@@ -2303,7 +2440,7 @@
         <v>35</v>
       </c>
       <c r="H4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I4" t="s">
         <v>36</v>
@@ -2344,13 +2481,13 @@
         <v>42535</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
         <v>18</v>
@@ -2362,10 +2499,10 @@
         <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s">
         <v>31</v>
@@ -2403,13 +2540,13 @@
         <v>42565</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
@@ -2421,7 +2558,7 @@
         <v>24</v>
       </c>
       <c r="H6" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I6" t="s">
         <v>25</v>
@@ -2462,13 +2599,13 @@
         <v>42580</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -2480,10 +2617,10 @@
         <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I7" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J7" t="s">
         <v>42</v>
@@ -2521,13 +2658,13 @@
         <v>42610</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
@@ -2539,13 +2676,13 @@
         <v>24</v>
       </c>
       <c r="H8" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I8" t="s">
         <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K8">
         <v>280</v>
@@ -2580,13 +2717,13 @@
         <v>42625</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>18</v>
@@ -2598,13 +2735,13 @@
         <v>24</v>
       </c>
       <c r="H9" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J9" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K9">
         <v>409</v>
@@ -2639,13 +2776,13 @@
         <v>42670</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
         <v>18</v>
@@ -2657,7 +2794,7 @@
         <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I10" t="s">
         <v>25</v>
@@ -2698,13 +2835,13 @@
         <v>42700</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -2716,7 +2853,7 @@
         <v>24</v>
       </c>
       <c r="H11" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I11" t="s">
         <v>25</v>
@@ -2757,13 +2894,13 @@
         <v>42745</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -2775,10 +2912,10 @@
         <v>19</v>
       </c>
       <c r="H12" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I12" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J12" t="s">
         <v>31</v>
@@ -2816,13 +2953,13 @@
         <v>42775</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
         <v>18</v>
@@ -2834,7 +2971,7 @@
         <v>29</v>
       </c>
       <c r="H13" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s">
         <v>25</v>
@@ -2875,13 +3012,13 @@
         <v>42865</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -2893,10 +3030,10 @@
         <v>29</v>
       </c>
       <c r="H14" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I14" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J14" t="s">
         <v>48</v>
@@ -2934,13 +3071,13 @@
         <v>42880</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -2952,13 +3089,13 @@
         <v>24</v>
       </c>
       <c r="H15" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I15" t="s">
         <v>36</v>
       </c>
       <c r="J15" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K15">
         <v>445</v>
@@ -2993,13 +3130,13 @@
         <v>42970</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
         <v>18</v>
@@ -3011,7 +3148,7 @@
         <v>29</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I16" t="s">
         <v>25</v>
@@ -3052,13 +3189,13 @@
         <v>43000</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
@@ -3070,10 +3207,10 @@
         <v>29</v>
       </c>
       <c r="H17" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I17" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J17" t="s">
         <v>31</v>
@@ -3111,13 +3248,13 @@
         <v>43060</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
@@ -3129,7 +3266,7 @@
         <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I18" t="s">
         <v>36</v>
@@ -3170,13 +3307,13 @@
         <v>43105</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E19" t="s">
         <v>28</v>
@@ -3188,10 +3325,10 @@
         <v>24</v>
       </c>
       <c r="H19" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I19" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J19" t="s">
         <v>42</v>
@@ -3229,13 +3366,13 @@
         <v>43165</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
         <v>18</v>
@@ -3247,10 +3384,10 @@
         <v>29</v>
       </c>
       <c r="H20" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I20" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J20" t="s">
         <v>42</v>
@@ -3288,13 +3425,13 @@
         <v>43195</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E21" t="s">
         <v>18</v>
@@ -3306,10 +3443,10 @@
         <v>29</v>
       </c>
       <c r="H21" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I21" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J21" t="s">
         <v>45</v>
@@ -3347,13 +3484,13 @@
         <v>43240</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s">
         <v>18</v>
@@ -3365,10 +3502,10 @@
         <v>29</v>
       </c>
       <c r="H22" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I22" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J22" t="s">
         <v>42</v>
@@ -3406,13 +3543,13 @@
         <v>43255</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E23" t="s">
         <v>28</v>
@@ -3424,10 +3561,10 @@
         <v>29</v>
       </c>
       <c r="H23" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I23" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J23" t="s">
         <v>48</v>
@@ -3465,13 +3602,13 @@
         <v>43315</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E24" t="s">
         <v>18</v>
@@ -3483,10 +3620,10 @@
         <v>29</v>
       </c>
       <c r="H24" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I24" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J24" t="s">
         <v>31</v>
@@ -3524,13 +3661,13 @@
         <v>43345</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E25" t="s">
         <v>18</v>
@@ -3542,10 +3679,10 @@
         <v>29</v>
       </c>
       <c r="H25" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I25" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J25" t="s">
         <v>42</v>
@@ -3583,13 +3720,13 @@
         <v>43375</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E26" t="s">
         <v>18</v>
@@ -3601,10 +3738,10 @@
         <v>19</v>
       </c>
       <c r="H26" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I26" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J26" t="s">
         <v>49</v>
@@ -3642,13 +3779,13 @@
         <v>43480</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E27" t="s">
         <v>28</v>
@@ -3660,10 +3797,10 @@
         <v>24</v>
       </c>
       <c r="H27" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I27" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J27" t="s">
         <v>42</v>
@@ -3701,13 +3838,13 @@
         <v>43600</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E28" t="s">
         <v>28</v>
@@ -3719,10 +3856,10 @@
         <v>29</v>
       </c>
       <c r="H28" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I28" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J28" t="s">
         <v>42</v>
@@ -3760,13 +3897,13 @@
         <v>43690</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E29" t="s">
         <v>18</v>
@@ -3778,7 +3915,7 @@
         <v>19</v>
       </c>
       <c r="H29" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I29" t="s">
         <v>25</v>
@@ -3819,13 +3956,13 @@
         <v>43750</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E30" t="s">
         <v>28</v>
@@ -3837,10 +3974,10 @@
         <v>29</v>
       </c>
       <c r="H30" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I30" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J30" t="s">
         <v>31</v>
@@ -3878,13 +4015,13 @@
         <v>43765</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E31" t="s">
         <v>28</v>
@@ -3896,7 +4033,7 @@
         <v>29</v>
       </c>
       <c r="H31" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I31" t="s">
         <v>25</v>
@@ -3937,13 +4074,13 @@
         <v>43795</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E32" t="s">
         <v>18</v>
@@ -3955,10 +4092,10 @@
         <v>19</v>
       </c>
       <c r="H32" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I32" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J32" t="s">
         <v>42</v>
@@ -3996,13 +4133,13 @@
         <v>43840</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E33" t="s">
         <v>28</v>
@@ -4014,13 +4151,13 @@
         <v>29</v>
       </c>
       <c r="H33" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I33" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J33" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K33">
         <v>339</v>
@@ -4055,13 +4192,13 @@
         <v>43885</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E34" t="s">
         <v>18</v>
@@ -4073,7 +4210,7 @@
         <v>24</v>
       </c>
       <c r="H34" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I34" t="s">
         <v>25</v>
@@ -4114,13 +4251,13 @@
         <v>43945</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E35" t="s">
         <v>28</v>
@@ -4132,7 +4269,7 @@
         <v>29</v>
       </c>
       <c r="H35" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I35" t="s">
         <v>25</v>
@@ -4173,13 +4310,13 @@
         <v>43990</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E36" t="s">
         <v>18</v>
@@ -4191,7 +4328,7 @@
         <v>29</v>
       </c>
       <c r="H36" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I36" t="s">
         <v>25</v>
@@ -4232,13 +4369,13 @@
         <v>44005</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E37" t="s">
         <v>18</v>
@@ -4250,7 +4387,7 @@
         <v>29</v>
       </c>
       <c r="H37" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I37" t="s">
         <v>25</v>
@@ -4291,13 +4428,13 @@
         <v>44020</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E38" t="s">
         <v>28</v>
@@ -4309,10 +4446,10 @@
         <v>29</v>
       </c>
       <c r="H38" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I38" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J38" t="s">
         <v>31</v>
@@ -4350,13 +4487,13 @@
         <v>44065</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E39" t="s">
         <v>28</v>
@@ -4368,7 +4505,7 @@
         <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I39" t="s">
         <v>39</v>
@@ -4409,13 +4546,13 @@
         <v>44080</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E40" t="s">
         <v>18</v>
@@ -4427,10 +4564,10 @@
         <v>19</v>
       </c>
       <c r="H40" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I40" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J40" t="s">
         <v>49</v>
@@ -4468,13 +4605,13 @@
         <v>44095</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E41" t="s">
         <v>28</v>
@@ -4486,13 +4623,13 @@
         <v>29</v>
       </c>
       <c r="H41" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I41" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J41" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K41">
         <v>411</v>
@@ -4527,13 +4664,13 @@
         <v>44125</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E42" t="s">
         <v>28</v>
@@ -4545,7 +4682,7 @@
         <v>24</v>
       </c>
       <c r="H42" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I42" t="s">
         <v>25</v>
@@ -4586,13 +4723,13 @@
         <v>44140</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E43" t="s">
         <v>28</v>
@@ -4604,10 +4741,10 @@
         <v>24</v>
       </c>
       <c r="H43" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I43" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J43" t="s">
         <v>42</v>
@@ -4645,13 +4782,13 @@
         <v>44155</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E44" t="s">
         <v>18</v>
@@ -4663,7 +4800,7 @@
         <v>19</v>
       </c>
       <c r="H44" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I44" t="s">
         <v>25</v>
@@ -4704,13 +4841,13 @@
         <v>44170</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E45" t="s">
         <v>28</v>
@@ -4722,10 +4859,10 @@
         <v>29</v>
       </c>
       <c r="H45" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I45" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J45" t="s">
         <v>42</v>
@@ -4763,13 +4900,13 @@
         <v>44185</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E46" t="s">
         <v>18</v>
@@ -4781,10 +4918,10 @@
         <v>19</v>
       </c>
       <c r="H46" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I46" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J46" t="s">
         <v>42</v>
@@ -4822,13 +4959,13 @@
         <v>44200</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E47" t="s">
         <v>18</v>
@@ -4840,13 +4977,13 @@
         <v>29</v>
       </c>
       <c r="H47" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I47" t="s">
         <v>25</v>
       </c>
       <c r="J47" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K47">
         <v>204</v>
@@ -4881,13 +5018,13 @@
         <v>44215</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E48" t="s">
         <v>28</v>
@@ -4899,7 +5036,7 @@
         <v>29</v>
       </c>
       <c r="H48" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I48" t="s">
         <v>25</v>
@@ -4940,13 +5077,13 @@
         <v>44230</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E49" t="s">
         <v>18</v>
@@ -4958,10 +5095,10 @@
         <v>29</v>
       </c>
       <c r="H49" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I49" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J49" t="s">
         <v>48</v>
@@ -4999,13 +5136,13 @@
         <v>44275</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E50" t="s">
         <v>28</v>
@@ -5017,13 +5154,13 @@
         <v>35</v>
       </c>
       <c r="H50" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I50" t="s">
         <v>25</v>
       </c>
       <c r="J50" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K50">
         <v>386</v>
@@ -5058,13 +5195,13 @@
         <v>44305</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E51" t="s">
         <v>28</v>
@@ -5076,13 +5213,13 @@
         <v>24</v>
       </c>
       <c r="H51" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I51" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J51" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K51">
         <v>465</v>
@@ -5117,13 +5254,13 @@
         <v>44350</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E52" t="s">
         <v>28</v>
@@ -5135,7 +5272,7 @@
         <v>24</v>
       </c>
       <c r="H52" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I52" t="s">
         <v>25</v>
@@ -5176,13 +5313,13 @@
         <v>44380</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E53" t="s">
         <v>28</v>
@@ -5194,13 +5331,13 @@
         <v>24</v>
       </c>
       <c r="H53" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I53" t="s">
         <v>36</v>
       </c>
       <c r="J53" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K53">
         <v>142</v>
@@ -5235,13 +5372,13 @@
         <v>44440</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E54" t="s">
         <v>18</v>
@@ -5253,10 +5390,10 @@
         <v>29</v>
       </c>
       <c r="H54" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I54" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J54" t="s">
         <v>42</v>
